--- a/originales/respuestas/2025/01. Calificadas/root/Lotería De Bogotá.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/root/Lotería De Bogotá.xlsx
@@ -505,7 +505,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -522,6 +522,15 @@
       <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <u/>
@@ -610,7 +619,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="28">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -668,14 +677,30 @@
     <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2137,11 +2162,17 @@
         <v>2.0778679313E10</v>
       </c>
       <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
+      <c r="K4" s="8">
+        <v>3.0</v>
+      </c>
       <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
+      <c r="M4" s="8">
+        <v>3.0</v>
+      </c>
       <c r="N4" s="6"/>
-      <c r="O4" s="6"/>
+      <c r="O4" s="8">
+        <v>3.0</v>
+      </c>
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
@@ -2188,11 +2219,17 @@
         <v>2.7194831795E10</v>
       </c>
       <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
+      <c r="K5" s="8">
+        <v>3.0</v>
+      </c>
       <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
+      <c r="M5" s="8">
+        <v>3.0</v>
+      </c>
       <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
+      <c r="O5" s="8">
+        <v>3.0</v>
+      </c>
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
@@ -2286,11 +2323,17 @@
         <v>0.0</v>
       </c>
       <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
+      <c r="K7" s="12">
+        <v>3.0</v>
+      </c>
       <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
+      <c r="M7" s="12">
+        <v>3.0</v>
+      </c>
       <c r="N7" s="10"/>
-      <c r="O7" s="10"/>
+      <c r="O7" s="12">
+        <v>3.0</v>
+      </c>
       <c r="P7" s="10"/>
       <c r="Q7" s="10"/>
       <c r="R7" s="10"/>
@@ -2388,11 +2431,17 @@
         <v>0.0</v>
       </c>
       <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
+      <c r="K9" s="8">
+        <v>3.0</v>
+      </c>
       <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
+      <c r="M9" s="8">
+        <v>3.0</v>
+      </c>
       <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
+      <c r="O9" s="8">
+        <v>3.0</v>
+      </c>
       <c r="P9" s="6"/>
       <c r="Q9" s="6"/>
       <c r="R9" s="6"/>
@@ -2490,11 +2539,17 @@
         <v>1.2010240353E10</v>
       </c>
       <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
+      <c r="K11" s="8">
+        <v>3.0</v>
+      </c>
       <c r="L11" s="6"/>
-      <c r="M11" s="6"/>
+      <c r="M11" s="8">
+        <v>3.0</v>
+      </c>
       <c r="N11" s="6"/>
-      <c r="O11" s="6"/>
+      <c r="O11" s="8">
+        <v>3.0</v>
+      </c>
       <c r="P11" s="6"/>
       <c r="Q11" s="6"/>
       <c r="R11" s="6"/>
@@ -2541,11 +2596,17 @@
         <v>1.2111384666E10</v>
       </c>
       <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
+      <c r="K12" s="12">
+        <v>3.0</v>
+      </c>
       <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
+      <c r="M12" s="12">
+        <v>3.0</v>
+      </c>
       <c r="N12" s="10"/>
-      <c r="O12" s="10"/>
+      <c r="O12" s="12">
+        <v>3.0</v>
+      </c>
       <c r="P12" s="10"/>
       <c r="Q12" s="10"/>
       <c r="R12" s="10"/>
@@ -2637,11 +2698,17 @@
         <v>0.0</v>
       </c>
       <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
+      <c r="K14" s="12">
+        <v>3.0</v>
+      </c>
       <c r="L14" s="10"/>
-      <c r="M14" s="10"/>
+      <c r="M14" s="12">
+        <v>3.0</v>
+      </c>
       <c r="N14" s="10"/>
-      <c r="O14" s="10"/>
+      <c r="O14" s="12">
+        <v>3.0</v>
+      </c>
       <c r="P14" s="10"/>
       <c r="Q14" s="10"/>
       <c r="R14" s="10"/>
@@ -2790,11 +2857,17 @@
         <v>0.0</v>
       </c>
       <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
+      <c r="K17" s="12">
+        <v>3.0</v>
+      </c>
       <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
+      <c r="M17" s="12">
+        <v>3.0</v>
+      </c>
       <c r="N17" s="10"/>
-      <c r="O17" s="10"/>
+      <c r="O17" s="12">
+        <v>3.0</v>
+      </c>
       <c r="P17" s="10"/>
       <c r="Q17" s="10"/>
       <c r="R17" s="10"/>
@@ -2841,11 +2914,17 @@
         <v>39.0</v>
       </c>
       <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
+      <c r="K18" s="8">
+        <v>3.0</v>
+      </c>
       <c r="L18" s="6"/>
-      <c r="M18" s="6"/>
+      <c r="M18" s="8">
+        <v>3.0</v>
+      </c>
       <c r="N18" s="6"/>
-      <c r="O18" s="6"/>
+      <c r="O18" s="8">
+        <v>3.0</v>
+      </c>
       <c r="P18" s="6"/>
       <c r="Q18" s="6"/>
       <c r="R18" s="6"/>
@@ -2892,11 +2971,17 @@
         <v>37.0</v>
       </c>
       <c r="J19" s="10"/>
-      <c r="K19" s="10"/>
+      <c r="K19" s="12">
+        <v>3.0</v>
+      </c>
       <c r="L19" s="10"/>
-      <c r="M19" s="10"/>
+      <c r="M19" s="12">
+        <v>3.0</v>
+      </c>
       <c r="N19" s="10"/>
-      <c r="O19" s="10"/>
+      <c r="O19" s="12">
+        <v>3.0</v>
+      </c>
       <c r="P19" s="10"/>
       <c r="Q19" s="10"/>
       <c r="R19" s="10"/>
@@ -2943,11 +3028,17 @@
         <v>3.0</v>
       </c>
       <c r="J20" s="6"/>
-      <c r="K20" s="6"/>
+      <c r="K20" s="8">
+        <v>3.0</v>
+      </c>
       <c r="L20" s="6"/>
-      <c r="M20" s="6"/>
+      <c r="M20" s="8">
+        <v>3.0</v>
+      </c>
       <c r="N20" s="6"/>
-      <c r="O20" s="6"/>
+      <c r="O20" s="8">
+        <v>3.0</v>
+      </c>
       <c r="P20" s="6"/>
       <c r="Q20" s="6"/>
       <c r="R20" s="6"/>
@@ -2994,11 +3085,17 @@
         <v>4.0</v>
       </c>
       <c r="J21" s="6"/>
-      <c r="K21" s="6"/>
+      <c r="K21" s="8">
+        <v>3.0</v>
+      </c>
       <c r="L21" s="6"/>
-      <c r="M21" s="6"/>
+      <c r="M21" s="8">
+        <v>3.0</v>
+      </c>
       <c r="N21" s="6"/>
-      <c r="O21" s="6"/>
+      <c r="O21" s="8">
+        <v>3.0</v>
+      </c>
       <c r="P21" s="6"/>
       <c r="Q21" s="6"/>
       <c r="R21" s="6"/>
@@ -3096,11 +3193,17 @@
         <v>10.0</v>
       </c>
       <c r="J23" s="10"/>
-      <c r="K23" s="10"/>
+      <c r="K23" s="12">
+        <v>3.0</v>
+      </c>
       <c r="L23" s="10"/>
-      <c r="M23" s="10"/>
+      <c r="M23" s="12">
+        <v>3.0</v>
+      </c>
       <c r="N23" s="10"/>
-      <c r="O23" s="10"/>
+      <c r="O23" s="12">
+        <v>3.0</v>
+      </c>
       <c r="P23" s="10"/>
       <c r="Q23" s="10"/>
       <c r="R23" s="10"/>
@@ -3147,11 +3250,17 @@
         <v>12.0</v>
       </c>
       <c r="J24" s="6"/>
-      <c r="K24" s="6"/>
+      <c r="K24" s="8">
+        <v>3.0</v>
+      </c>
       <c r="L24" s="6"/>
-      <c r="M24" s="6"/>
+      <c r="M24" s="8">
+        <v>3.0</v>
+      </c>
       <c r="N24" s="6"/>
-      <c r="O24" s="6"/>
+      <c r="O24" s="8">
+        <v>3.0</v>
+      </c>
       <c r="P24" s="6"/>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
@@ -3198,11 +3307,17 @@
         <v>6.0</v>
       </c>
       <c r="J25" s="10"/>
-      <c r="K25" s="10"/>
+      <c r="K25" s="12">
+        <v>3.0</v>
+      </c>
       <c r="L25" s="10"/>
-      <c r="M25" s="10"/>
+      <c r="M25" s="12">
+        <v>3.0</v>
+      </c>
       <c r="N25" s="10"/>
-      <c r="O25" s="10"/>
+      <c r="O25" s="12">
+        <v>3.0</v>
+      </c>
       <c r="P25" s="10"/>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
@@ -3249,11 +3364,17 @@
         <v>6.0</v>
       </c>
       <c r="J26" s="6"/>
-      <c r="K26" s="6"/>
+      <c r="K26" s="8">
+        <v>3.0</v>
+      </c>
       <c r="L26" s="6"/>
-      <c r="M26" s="6"/>
+      <c r="M26" s="8">
+        <v>3.0</v>
+      </c>
       <c r="N26" s="6"/>
-      <c r="O26" s="6"/>
+      <c r="O26" s="8">
+        <v>3.0</v>
+      </c>
       <c r="P26" s="6"/>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -4480,7 +4601,9 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="31" width="10.71"/>
+    <col customWidth="1" min="1" max="8" width="10.71"/>
+    <col customWidth="1" min="9" max="9" width="42.14"/>
+    <col customWidth="1" min="10" max="31" width="10.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="43.5" customHeight="1">
@@ -4814,15 +4937,25 @@
         <v>96</v>
       </c>
       <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
+      <c r="K7" s="8">
+        <v>1.0</v>
+      </c>
       <c r="L7" s="14"/>
-      <c r="M7" s="6"/>
+      <c r="M7" s="8">
+        <v>1.0</v>
+      </c>
       <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
+      <c r="O7" s="8">
+        <v>1.0</v>
+      </c>
       <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
+      <c r="Q7" s="8">
+        <v>2.0</v>
+      </c>
       <c r="R7" s="6"/>
-      <c r="S7" s="15"/>
+      <c r="S7" s="18">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="8" ht="126.75" customHeight="1">
       <c r="A8" s="6" t="s">
@@ -4853,15 +4986,25 @@
         <v>99</v>
       </c>
       <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="14"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
-      <c r="Q8" s="6"/>
-      <c r="R8" s="6"/>
-      <c r="S8" s="15"/>
+      <c r="K8" s="19">
+        <v>3.0</v>
+      </c>
+      <c r="L8" s="20"/>
+      <c r="M8" s="21">
+        <v>4.0</v>
+      </c>
+      <c r="N8" s="20"/>
+      <c r="O8" s="21">
+        <v>4.0</v>
+      </c>
+      <c r="P8" s="20"/>
+      <c r="Q8" s="19">
+        <v>3.0</v>
+      </c>
+      <c r="R8" s="20"/>
+      <c r="S8" s="22">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="9" ht="126.75" customHeight="1">
       <c r="A9" s="10" t="s">
@@ -4892,15 +5035,25 @@
         <v>102</v>
       </c>
       <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
-      <c r="O9" s="10"/>
-      <c r="P9" s="10"/>
-      <c r="Q9" s="10"/>
-      <c r="R9" s="10"/>
-      <c r="S9" s="17"/>
+      <c r="K9" s="21">
+        <v>4.0</v>
+      </c>
+      <c r="L9" s="20"/>
+      <c r="M9" s="19">
+        <v>3.0</v>
+      </c>
+      <c r="N9" s="20"/>
+      <c r="O9" s="21">
+        <v>4.0</v>
+      </c>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="19">
+        <v>3.0</v>
+      </c>
+      <c r="R9" s="20"/>
+      <c r="S9" s="22">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="10" ht="126.75" customHeight="1">
       <c r="A10" s="6" t="s">
@@ -4931,15 +5084,25 @@
         <v>105</v>
       </c>
       <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
+      <c r="K10" s="8">
+        <v>3.0</v>
+      </c>
       <c r="L10" s="14"/>
-      <c r="M10" s="6"/>
+      <c r="M10" s="8">
+        <v>3.0</v>
+      </c>
       <c r="N10" s="6"/>
-      <c r="O10" s="6"/>
+      <c r="O10" s="8">
+        <v>4.0</v>
+      </c>
       <c r="P10" s="6"/>
-      <c r="Q10" s="6"/>
+      <c r="Q10" s="8">
+        <v>3.0</v>
+      </c>
       <c r="R10" s="6"/>
-      <c r="S10" s="15"/>
+      <c r="S10" s="18">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="11" ht="126.75" customHeight="1">
       <c r="A11" s="10" t="s">
@@ -4970,15 +5133,25 @@
         <v>108</v>
       </c>
       <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
+      <c r="K11" s="12">
+        <v>2.0</v>
+      </c>
       <c r="L11" s="16"/>
-      <c r="M11" s="10"/>
+      <c r="M11" s="12">
+        <v>3.0</v>
+      </c>
       <c r="N11" s="10"/>
-      <c r="O11" s="10"/>
+      <c r="O11" s="12">
+        <v>3.0</v>
+      </c>
       <c r="P11" s="10"/>
-      <c r="Q11" s="10"/>
-      <c r="R11" s="10"/>
-      <c r="S11" s="17"/>
+      <c r="Q11" s="12">
+        <v>2.0</v>
+      </c>
+      <c r="R11" s="12"/>
+      <c r="S11" s="23">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="12" ht="126.75" customHeight="1">
       <c r="A12" s="10" t="s">
@@ -5009,15 +5182,25 @@
         <v>111</v>
       </c>
       <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
+      <c r="K12" s="12">
+        <v>3.0</v>
+      </c>
       <c r="L12" s="16"/>
-      <c r="M12" s="10"/>
+      <c r="M12" s="12">
+        <v>3.0</v>
+      </c>
       <c r="N12" s="10"/>
-      <c r="O12" s="10"/>
+      <c r="O12" s="12">
+        <v>3.0</v>
+      </c>
       <c r="P12" s="10"/>
-      <c r="Q12" s="10"/>
+      <c r="Q12" s="12">
+        <v>4.0</v>
+      </c>
       <c r="R12" s="10"/>
-      <c r="S12" s="17"/>
+      <c r="S12" s="23">
+        <v>4.0</v>
+      </c>
     </row>
     <row r="13" ht="126.75" customHeight="1">
       <c r="A13" s="6" t="s">
@@ -5048,15 +5231,25 @@
         <v>114</v>
       </c>
       <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="14"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="6"/>
-      <c r="Q13" s="6"/>
-      <c r="R13" s="6"/>
-      <c r="S13" s="15"/>
+      <c r="K13" s="19">
+        <v>3.0</v>
+      </c>
+      <c r="L13" s="20"/>
+      <c r="M13" s="19">
+        <v>3.0</v>
+      </c>
+      <c r="N13" s="20"/>
+      <c r="O13" s="19">
+        <v>3.0</v>
+      </c>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="19">
+        <v>4.0</v>
+      </c>
+      <c r="R13" s="20"/>
+      <c r="S13" s="22">
+        <v>4.0</v>
+      </c>
     </row>
     <row r="14" ht="126.75" customHeight="1">
       <c r="A14" s="6" t="s">
@@ -5087,15 +5280,25 @@
         <v>117</v>
       </c>
       <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
+      <c r="K14" s="8">
+        <v>3.0</v>
+      </c>
       <c r="L14" s="14"/>
-      <c r="M14" s="6"/>
+      <c r="M14" s="8">
+        <v>4.0</v>
+      </c>
       <c r="N14" s="6"/>
-      <c r="O14" s="6"/>
+      <c r="O14" s="8">
+        <v>3.0</v>
+      </c>
       <c r="P14" s="6"/>
-      <c r="Q14" s="6"/>
+      <c r="Q14" s="8">
+        <v>3.0</v>
+      </c>
       <c r="R14" s="6"/>
-      <c r="S14" s="15"/>
+      <c r="S14" s="18">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="15" ht="126.75" customHeight="1">
       <c r="A15" s="10" t="s">
@@ -5126,15 +5329,25 @@
         <v>120</v>
       </c>
       <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
+      <c r="K15" s="12">
+        <v>3.0</v>
+      </c>
       <c r="L15" s="16"/>
-      <c r="M15" s="10"/>
+      <c r="M15" s="12">
+        <v>3.0</v>
+      </c>
       <c r="N15" s="10"/>
-      <c r="O15" s="10"/>
+      <c r="O15" s="12">
+        <v>3.0</v>
+      </c>
       <c r="P15" s="10"/>
-      <c r="Q15" s="10"/>
+      <c r="Q15" s="12">
+        <v>3.0</v>
+      </c>
       <c r="R15" s="10"/>
-      <c r="S15" s="17"/>
+      <c r="S15" s="23">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="16" ht="126.75" customHeight="1">
       <c r="A16" s="6" t="s">
@@ -6404,15 +6617,25 @@
         <v>137</v>
       </c>
       <c r="J3" s="15"/>
-      <c r="K3" s="15"/>
+      <c r="K3" s="18">
+        <v>4.0</v>
+      </c>
       <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
+      <c r="M3" s="18">
+        <v>4.0</v>
+      </c>
       <c r="N3" s="15"/>
-      <c r="O3" s="15"/>
+      <c r="O3" s="18">
+        <v>4.0</v>
+      </c>
       <c r="P3" s="15"/>
-      <c r="Q3" s="15"/>
+      <c r="Q3" s="18">
+        <v>4.0</v>
+      </c>
       <c r="R3" s="15"/>
-      <c r="S3" s="15"/>
+      <c r="S3" s="18">
+        <v>4.0</v>
+      </c>
     </row>
     <row r="4" ht="14.25" customHeight="1"/>
     <row r="5" ht="14.25" customHeight="1"/>
@@ -7532,7 +7755,7 @@
       <c r="K2" s="18">
         <v>2.0</v>
       </c>
-      <c r="L2" s="19"/>
+      <c r="L2" s="24"/>
       <c r="M2" s="18">
         <v>3.0</v>
       </c>
@@ -7572,15 +7795,25 @@
         <v>145</v>
       </c>
       <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
-      <c r="L3" s="20"/>
-      <c r="M3" s="17"/>
+      <c r="K3" s="23">
+        <v>3.0</v>
+      </c>
+      <c r="L3" s="25"/>
+      <c r="M3" s="23">
+        <v>4.0</v>
+      </c>
       <c r="N3" s="17"/>
-      <c r="O3" s="17"/>
+      <c r="O3" s="23">
+        <v>4.0</v>
+      </c>
       <c r="P3" s="17"/>
-      <c r="Q3" s="17"/>
+      <c r="Q3" s="23">
+        <v>3.0</v>
+      </c>
       <c r="R3" s="17"/>
-      <c r="S3" s="17"/>
+      <c r="S3" s="23">
+        <v>4.0</v>
+      </c>
     </row>
     <row r="4" ht="126.75" customHeight="1">
       <c r="A4" s="17" t="s">
@@ -7603,12 +7836,12 @@
       <c r="H4" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="I4" s="21" t="s">
+      <c r="I4" s="26" t="s">
         <v>147</v>
       </c>
       <c r="J4" s="17"/>
       <c r="K4" s="17"/>
-      <c r="L4" s="20"/>
+      <c r="L4" s="25"/>
       <c r="M4" s="17"/>
       <c r="N4" s="17"/>
       <c r="O4" s="17"/>
@@ -7644,15 +7877,25 @@
         <v>150</v>
       </c>
       <c r="J5" s="17"/>
-      <c r="K5" s="17"/>
-      <c r="L5" s="20"/>
-      <c r="M5" s="17"/>
+      <c r="K5" s="23">
+        <v>3.0</v>
+      </c>
+      <c r="L5" s="25"/>
+      <c r="M5" s="23">
+        <v>3.0</v>
+      </c>
       <c r="N5" s="17"/>
-      <c r="O5" s="17"/>
+      <c r="O5" s="23">
+        <v>4.0</v>
+      </c>
       <c r="P5" s="17"/>
-      <c r="Q5" s="17"/>
+      <c r="Q5" s="23">
+        <v>2.0</v>
+      </c>
       <c r="R5" s="17"/>
-      <c r="S5" s="17"/>
+      <c r="S5" s="23">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="6" ht="126.75" customHeight="1">
       <c r="A6" s="17" t="s">
@@ -7681,15 +7924,25 @@
         <v>153</v>
       </c>
       <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="20"/>
-      <c r="M6" s="17"/>
+      <c r="K6" s="23">
+        <v>0.0</v>
+      </c>
+      <c r="L6" s="25"/>
+      <c r="M6" s="23">
+        <v>0.0</v>
+      </c>
       <c r="N6" s="17"/>
-      <c r="O6" s="17"/>
+      <c r="O6" s="23">
+        <v>0.0</v>
+      </c>
       <c r="P6" s="17"/>
-      <c r="Q6" s="17"/>
+      <c r="Q6" s="23">
+        <v>0.0</v>
+      </c>
       <c r="R6" s="17"/>
-      <c r="S6" s="17"/>
+      <c r="S6" s="23">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="7" ht="126.75" customHeight="1">
       <c r="A7" s="15" t="s">
@@ -7720,15 +7973,25 @@
         <v>25</v>
       </c>
       <c r="J7" s="15"/>
-      <c r="K7" s="18"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="18"/>
+      <c r="K7" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="L7" s="27"/>
+      <c r="M7" s="18">
+        <v>0.0</v>
+      </c>
       <c r="N7" s="15"/>
-      <c r="O7" s="18"/>
+      <c r="O7" s="18">
+        <v>0.0</v>
+      </c>
       <c r="P7" s="15"/>
-      <c r="Q7" s="18"/>
+      <c r="Q7" s="18">
+        <v>0.0</v>
+      </c>
       <c r="R7" s="15"/>
-      <c r="S7" s="15"/>
+      <c r="S7" s="18">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="8" ht="14.25" customHeight="1"/>
     <row r="9" ht="14.25" customHeight="1"/>
